--- a/site/assets/examples/07-create-a-pivot-table.xlsx
+++ b/site/assets/examples/07-create-a-pivot-table.xlsx
@@ -405,7 +405,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Grand Total</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B8">

--- a/site/assets/examples/07-create-a-pivot-table.xlsx
+++ b/site/assets/examples/07-create-a-pivot-table.xlsx
@@ -126,8 +126,8 @@
     </cacheField>
     <cacheField name="category" numFmtId="0">
       <sharedItems containsString="1" count="2">
+        <s v="Drinks"/>
         <s v="Food"/>
-        <s v="Drinks"/>
       </sharedItems>
     </cacheField>
     <cacheField name="sales" numFmtId="0">
@@ -141,13 +141,18 @@
 <pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6">
   <r>
     <s v="North"/>
+    <s v="Drinks"/>
+    <n v="180"/>
+  </r>
+  <r>
+    <s v="North"/>
     <s v="Food"/>
     <n v="420"/>
   </r>
   <r>
-    <s v="North"/>
+    <s v="South"/>
     <s v="Drinks"/>
-    <n v="180"/>
+    <n v="220"/>
   </r>
   <r>
     <s v="South"/>
@@ -155,26 +160,21 @@
     <n v="510"/>
   </r>
   <r>
-    <s v="South"/>
+    <s v="West"/>
     <s v="Drinks"/>
-    <n v="220"/>
+    <n v="260"/>
   </r>
   <r>
     <s v="West"/>
     <s v="Food"/>
     <n v="390"/>
   </r>
-  <r>
-    <s v="West"/>
-    <s v="Drinks"/>
-    <n v="260"/>
-  </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SalesByRegion" cacheId="1" dataCaption="Values" grandTotalCaption="Grand Total" updatedVersion="8" minRefreshableVersion="3" createdVersion="3" useAutoFormatting="1" itemPrintTitles="1" indent="0" compact="1" compactData="1" rowGrandTotals="1" colGrandTotals="1">
-  <location ref="A4:C8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <location ref="A4:D8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField axis="axisRow" showAll="0">
       <items count="1">
@@ -240,11 +240,11 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Drinks</t>
         </is>
       </c>
       <c r="C2" s="3">
-        <v>420</v>
+        <v>180</v>
       </c>
     </row>
     <row r="3">
@@ -255,11 +255,11 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Drinks</t>
+          <t>Food</t>
         </is>
       </c>
       <c r="C3" s="3">
-        <v>180</v>
+        <v>420</v>
       </c>
     </row>
     <row r="4">
@@ -270,11 +270,11 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Drinks</t>
         </is>
       </c>
       <c r="C4" s="3">
-        <v>510</v>
+        <v>220</v>
       </c>
     </row>
     <row r="5">
@@ -285,11 +285,11 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Drinks</t>
+          <t>Food</t>
         </is>
       </c>
       <c r="C5" s="3">
-        <v>220</v>
+        <v>510</v>
       </c>
     </row>
     <row r="6">
@@ -300,11 +300,11 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Drinks</t>
         </is>
       </c>
       <c r="C6" s="3">
-        <v>390</v>
+        <v>260</v>
       </c>
     </row>
     <row r="7">
@@ -315,11 +315,11 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Drinks</t>
+          <t>Food</t>
         </is>
       </c>
       <c r="C7" s="3">
-        <v>260</v>
+        <v>390</v>
       </c>
     </row>
   </sheetData>
@@ -329,7 +329,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -342,7 +342,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>A native PivotTable with cached source records and refresh-on-open support.</t>
+          <t>Native PivotTable with cached values and refresh-on-open support.</t>
         </is>
       </c>
     </row>
@@ -362,6 +362,11 @@
           <t>Food</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Grand Total</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -370,10 +375,13 @@
         </is>
       </c>
       <c r="B5">
+        <v>180</v>
+      </c>
+      <c r="C5">
         <v>420</v>
       </c>
-      <c r="C5">
-        <v>180</v>
+      <c r="D5">
+        <v>600</v>
       </c>
     </row>
     <row r="6">
@@ -383,10 +391,13 @@
         </is>
       </c>
       <c r="B6">
+        <v>220</v>
+      </c>
+      <c r="C6">
         <v>510</v>
       </c>
-      <c r="C6">
-        <v>220</v>
+      <c r="D6">
+        <v>730</v>
       </c>
     </row>
     <row r="7">
@@ -396,10 +407,13 @@
         </is>
       </c>
       <c r="B7">
+        <v>260</v>
+      </c>
+      <c r="C7">
         <v>390</v>
       </c>
-      <c r="C7">
-        <v>260</v>
+      <c r="D7">
+        <v>650</v>
       </c>
     </row>
     <row r="8">
@@ -409,10 +423,13 @@
         </is>
       </c>
       <c r="B8">
+        <v>660</v>
+      </c>
+      <c r="C8">
         <v>1320</v>
       </c>
-      <c r="C8">
-        <v>660</v>
+      <c r="D8">
+        <v>1980</v>
       </c>
     </row>
   </sheetData>
